--- a/etf_holdings/2026-09-15_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.24%2380</t>
+          <t>+0.21%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.55%4560</t>
+          <t>-2.85%4430</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4560</v>
+        <v>4430</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.73%2270</t>
+          <t>+1.98%2315</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2270</v>
+        <v>2315</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.85%703</t>
+          <t>+1.42%713</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>+1.42%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>703</v>
+        <v>713</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-5.2%437.5</t>
+          <t>+2.25%454</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>+2.25%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>437.5</v>
+        <v>454</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.75%11990</t>
+          <t>-2.29%11715</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>11990</v>
+        <v>11715</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.63%962</t>
+          <t>-7.48%890</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-7.48%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>962</v>
+        <v>890</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.93%2140</t>
+          <t>-2.8%2080</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2140</v>
+        <v>2080</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0%5620</t>
+          <t>-2.77%5440</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5620</v>
+        <v>5440</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.37%5345</t>
+          <t>-4.3%5115</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+4.43%1415</t>
+          <t>-2.52%1355</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+4.43%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1415</v>
+        <v>1355</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.11%489.5</t>
+          <t>-2.45%477.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>489.5</v>
+        <v>477.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-9.98%5995</t>
+          <t>+1%6055</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.98%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5995</v>
+        <v>6055</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.78%3310</t>
+          <t>-5.89%3115</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-5.89%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3310</v>
+        <v>3115</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:49</t>
+          <t>2026-09-15 19:51:50</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.53%1875</t>
+          <t>-1.87%1840</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1875</v>
+        <v>1840</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.64%902</t>
+          <t>+1.56%914</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.56%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.59%670</t>
+          <t>+2.24%685</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.18%277.5</t>
+          <t>-1.26%274</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>277.5</v>
+        <v>274</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+3.88%535</t>
+          <t>-2.8%520</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+3.88%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.42%142.5</t>
+          <t>-2.81%138.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>142.5</v>
+        <v>138.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.43%181</t>
+          <t>+0.83%182.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>181</v>
+        <v>182.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.53%187.5</t>
+          <t>+1.33%190</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>187.5</v>
+        <v>190</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-4.36%17885</t>
+          <t>-2.56%17520</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>17885</v>
+        <v>17520</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-2.98%683</t>
+          <t>-2.78%664</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2.98%</t>
+          <t>-2.78%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>683</v>
+        <v>664</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.68%176</t>
+          <t>-0.28%176</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.43%344</t>
+          <t>-0.29%343</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.43%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.15%1365</t>
+          <t>-2.84%1370</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.78%253</t>
+          <t>0%253</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-3.58%86.1</t>
+          <t>-0.78%89.4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.58%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>86.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:50</t>
+          <t>2026-09-15 19:52:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.97%612</t>
+          <t>-3.27%592</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-3.51%165</t>
+          <t>-1.53%160.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.51%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>165</v>
+        <v>160.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.31%163.5</t>
+          <t>-2.75%159</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-2.75%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>163.5</v>
+        <v>159</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.72%537</t>
+          <t>-3.91%516</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.72%</t>
+          <t>-3.91%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.42%119</t>
+          <t>-1.68%117</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.55%271.5</t>
+          <t>-1.29%268</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>271.5</v>
+        <v>268</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+1.01%150.5</t>
+          <t>-1.66%148</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>150.5</v>
+        <v>148</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-7.14%1235</t>
+          <t>-1.21%1220</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-7.14%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1235</v>
+        <v>1220</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.13%403.5</t>
+          <t>+1.86%411</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>403.5</v>
+        <v>411</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-3.24%836</t>
+          <t>-1.41%837</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.24%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.26%234.5</t>
+          <t>-2.77%228</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.26%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>234.5</v>
+        <v>228</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-5.49%2580</t>
+          <t>-3.85%2625</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.49%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2580</v>
+        <v>2625</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-3.31%1170</t>
+          <t>-2.65%1100</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1170</v>
+        <v>1100</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+1.76%520</t>
+          <t>-0.38%518</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+1.76%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.14%70.8</t>
+          <t>-3.53%68.3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>70.8</v>
+        <v>68.3</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:51</t>
+          <t>2026-09-15 19:52:13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.86%294.5</t>
+          <t>-1.19%291</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>294.5</v>
+        <v>291</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:53</t>
+          <t>2026-09-15 19:52:24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+1.27%119.5</t>
+          <t>-2.09%117</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>-2.09%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>119.5</v>
+        <v>117</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:53</t>
+          <t>2026-09-15 19:52:24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+2.45%50.2</t>
+          <t>-1.49%49.45</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+2.45%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>50.2</v>
+        <v>49.45</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:53</t>
+          <t>2026-09-15 19:52:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.62%241</t>
+          <t>-2.07%236</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:53</t>
+          <t>2026-09-15 19:52:24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-7.03%1190</t>
+          <t>+1.26%1205</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-7.03%</t>
+          <t>+1.26%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1190</v>
+        <v>1205</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:53</t>
+          <t>2026-09-15 19:52:24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-1.37%46.85</t>
+          <t>0%46.85</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:53</t>
+          <t>2026-09-15 19:52:24</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>+4.58%6400</t>
+          <t>-5.7%6035</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>6400</v>
+        <v>6035</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:53</t>
+          <t>2026-09-15 19:52:24</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-0.58%172.5</t>
+          <t>-0.87%171</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>172.5</v>
+        <v>171</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:53</t>
+          <t>2026-09-15 19:52:24</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-6.91%485</t>
+          <t>-6.95%482</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-6.91%</t>
+          <t>-6.95%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:53</t>
+          <t>2026-09-15 19:52:24</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3742,16 +3742,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-2.11%697</t>
+          <t>-0.43%694</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-2.11%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:53</t>
+          <t>2026-09-15 19:52:24</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3803,16 +3803,16 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+1.55%52.5</t>
+          <t>-1.33%51.8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>-1.33%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>52.5</v>
+        <v>51.8</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:53</t>
+          <t>2026-09-15 19:52:24</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,16 +3864,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>+3.7%154</t>
+          <t>-1.95%151</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>+3.7%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-15_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:50</t>
+          <t>2026-09-15 21:12:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:02</t>
+          <t>2026-09-15 21:12:11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:13</t>
+          <t>2026-09-15 21:12:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:24</t>
+          <t>2026-09-15 21:12:14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:24</t>
+          <t>2026-09-15 21:12:14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:24</t>
+          <t>2026-09-15 21:12:14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:24</t>
+          <t>2026-09-15 21:12:14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:24</t>
+          <t>2026-09-15 21:12:14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:24</t>
+          <t>2026-09-15 21:12:14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:24</t>
+          <t>2026-09-15 21:12:14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:24</t>
+          <t>2026-09-15 21:12:14</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:24</t>
+          <t>2026-09-15 21:12:14</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:24</t>
+          <t>2026-09-15 21:12:14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-15 19:52:24</t>
+          <t>2026-09-15 21:12:14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/etf_holdings/2026-09-15_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:09</t>
+          <t>2026-09-15 22:22:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:11</t>
+          <t>2026-09-15 22:22:28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:12</t>
+          <t>2026-09-15 22:22:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:14</t>
+          <t>2026-09-15 22:22:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:14</t>
+          <t>2026-09-15 22:22:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:14</t>
+          <t>2026-09-15 22:22:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:14</t>
+          <t>2026-09-15 22:22:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:14</t>
+          <t>2026-09-15 22:22:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:14</t>
+          <t>2026-09-15 22:22:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:14</t>
+          <t>2026-09-15 22:22:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:14</t>
+          <t>2026-09-15 22:22:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:14</t>
+          <t>2026-09-15 22:22:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:14</t>
+          <t>2026-09-15 22:22:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-15 21:12:14</t>
+          <t>2026-09-15 22:22:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">

--- a/etf_holdings/2026-09-15_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:26</t>
+          <t>2026-09-15 22:27:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:28</t>
+          <t>2026-09-15 22:28:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:29</t>
+          <t>2026-09-15 22:28:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:30</t>
+          <t>2026-09-15 22:28:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:30</t>
+          <t>2026-09-15 22:28:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:30</t>
+          <t>2026-09-15 22:28:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:30</t>
+          <t>2026-09-15 22:28:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:30</t>
+          <t>2026-09-15 22:28:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:30</t>
+          <t>2026-09-15 22:28:23</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:30</t>
+          <t>2026-09-15 22:28:23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:30</t>
+          <t>2026-09-15 22:28:23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:30</t>
+          <t>2026-09-15 22:28:23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:30</t>
+          <t>2026-09-15 22:28:23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-15 22:22:30</t>
+          <t>2026-09-15 22:28:23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
